--- a/educhrono-backend/app/templates/faculty-load_template_new.xlsx
+++ b/educhrono-backend/app/templates/faculty-load_template_new.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono-backend\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono\educhrono-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3847A05C-0198-4D9F-B994-ACC76DBA2387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0651D46-6C46-4F78-AB46-31AF5FFF5254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19260" windowHeight="10800" xr2:uid="{79F6FE28-0A33-4AE2-A138-C517667A5611}"/>
+    <workbookView xWindow="100" yWindow="0" windowWidth="19100" windowHeight="10800" xr2:uid="{79F6FE28-0A33-4AE2-A138-C517667A5611}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -254,6 +254,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,15 +598,15 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="1.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="1.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.26953125" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -655,24 +661,23 @@
       <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="1">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="F2" s="4">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
         <v>0</v>
       </c>
       <c r="K2">
-        <f>SUM(F2,G2*2,H2*2,I2*2,J2)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -691,24 +696,23 @@
       <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="1">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="F3" s="4">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="1">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K10" si="0">SUM(F3,G3*2,H3*2,I3*2,J3)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -727,24 +731,24 @@
       <c r="E4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ref="K4:K10" si="0">SUM(F4,G4*2,H4*2,I4*2,J4)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -763,24 +767,24 @@
       <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="1">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="F5" s="4">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="1">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
         <v>0</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -799,19 +803,19 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
         <v>0</v>
       </c>
       <c r="K6">
@@ -835,24 +839,23 @@
       <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F7" s="4">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
         <v>1</v>
       </c>
-      <c r="H7" s="1">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -871,24 +874,24 @@
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>3</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
         <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -907,19 +910,19 @@
       <c r="E9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
         <v>2</v>
       </c>
       <c r="K9">
@@ -943,19 +946,19 @@
       <c r="E10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
         <v>3</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="4">
         <v>0</v>
       </c>
       <c r="K10">

--- a/educhrono-backend/app/templates/faculty-load_template_new.xlsx
+++ b/educhrono-backend/app/templates/faculty-load_template_new.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\FunctionX\educhrono\educhrono-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0651D46-6C46-4F78-AB46-31AF5FFF5254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B10DA9-4F05-49A1-859C-812DE02FD640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="100" yWindow="0" windowWidth="19100" windowHeight="10800" xr2:uid="{79F6FE28-0A33-4AE2-A138-C517667A5611}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -645,7 +648,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -662,7 +665,7 @@
         <v>33</v>
       </c>
       <c r="F2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
@@ -677,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -697,7 +700,7 @@
         <v>29</v>
       </c>
       <c r="F3" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="4">
         <v>1</v>
@@ -751,7 +754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -768,7 +771,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4">
         <v>1</v>
@@ -783,11 +786,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -804,7 +806,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -820,10 +822,10 @@
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -840,10 +842,10 @@
         <v>13</v>
       </c>
       <c r="F7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4">
         <v>1</v>
@@ -855,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -878,7 +880,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
@@ -890,8 +892,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
